--- a/2025/Code MAGASIN Business Central.xlsx
+++ b/2025/Code MAGASIN Business Central.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231FEF57-3A71-4E16-B6A1-4122818F21B3}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA412B8-9424-43D8-A262-F175ACCCC7F5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2760" yWindow="2760" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -487,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -514,7 +514,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -796,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Feuil1"/>
+  <sheetPr codeName="Feuil1" filterMode="1"/>
   <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -816,7 +815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>103</v>
       </c>
@@ -827,7 +826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>104</v>
       </c>
@@ -838,7 +837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>108</v>
       </c>
@@ -849,7 +848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>114</v>
       </c>
@@ -860,7 +859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>119</v>
       </c>
@@ -871,7 +870,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>125</v>
       </c>
@@ -882,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>131</v>
       </c>
@@ -893,7 +892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>133</v>
       </c>
@@ -904,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>134</v>
       </c>
@@ -915,7 +914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>135</v>
       </c>
@@ -926,7 +925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>136</v>
       </c>
@@ -937,7 +936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>137</v>
       </c>
@@ -948,7 +947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>138</v>
       </c>
@@ -959,7 +958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>139</v>
       </c>
@@ -970,7 +969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>142</v>
       </c>
@@ -981,7 +980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>205</v>
       </c>
@@ -992,7 +991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>207</v>
       </c>
@@ -1003,7 +1002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>301</v>
       </c>
@@ -1014,7 +1013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>304</v>
       </c>
@@ -1025,7 +1024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>305</v>
       </c>
@@ -1036,7 +1035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>306</v>
       </c>
@@ -1047,7 +1046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>307</v>
       </c>
@@ -1058,7 +1057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>308</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>309</v>
       </c>
@@ -1080,7 +1079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>316</v>
       </c>
@@ -1091,7 +1090,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>317</v>
       </c>
@@ -1102,7 +1101,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>318</v>
       </c>
@@ -1113,7 +1112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>319</v>
       </c>
@@ -1124,7 +1123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>414</v>
       </c>
@@ -1135,7 +1134,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>102</v>
       </c>
@@ -1146,7 +1145,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>106</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>107</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>113</v>
       </c>
@@ -1179,7 +1178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>120</v>
       </c>
@@ -1188,7 +1187,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>128</v>
       </c>
@@ -1199,7 +1198,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>129</v>
       </c>
@@ -1210,7 +1209,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>130</v>
       </c>
@@ -1221,7 +1220,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>132</v>
       </c>
@@ -1232,7 +1231,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>141</v>
       </c>
@@ -1243,7 +1242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>145</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>201</v>
       </c>
@@ -1263,7 +1262,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>202</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>203</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>204</v>
       </c>
@@ -1296,7 +1295,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>206</v>
       </c>
@@ -1307,7 +1306,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>208</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>209</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>210</v>
       </c>
@@ -1340,7 +1339,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>213</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>214</v>
       </c>
@@ -1362,7 +1361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>217</v>
       </c>
@@ -1373,7 +1372,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>218</v>
       </c>
@@ -1384,7 +1383,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>220</v>
       </c>
@@ -1395,7 +1394,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>303</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>311</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>401</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>402</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>404</v>
       </c>
@@ -1461,7 +1460,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>405</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>412</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>415</v>
       </c>
@@ -1514,7 +1513,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>501</v>
       </c>
@@ -1525,7 +1524,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>502</v>
       </c>
@@ -1536,7 +1535,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>503</v>
       </c>
@@ -1547,7 +1546,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>504</v>
       </c>
@@ -1558,7 +1557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>506</v>
       </c>
@@ -1569,7 +1568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>507</v>
       </c>
@@ -1580,7 +1579,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>508</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>509</v>
       </c>
@@ -1602,7 +1601,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>515</v>
       </c>
@@ -1611,7 +1610,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>517</v>
       </c>
@@ -1622,7 +1621,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>518</v>
       </c>
@@ -1633,7 +1632,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>519</v>
       </c>
@@ -1644,7 +1643,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>521</v>
       </c>
@@ -1653,7 +1652,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>523</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>525</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>140</v>
       </c>
@@ -1686,7 +1685,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>111</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>112</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>117</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>116</v>
       </c>
@@ -1730,7 +1729,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>121</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>122</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>215</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>219</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>312</v>
       </c>
@@ -1785,7 +1784,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>313</v>
       </c>
@@ -1796,7 +1795,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>320</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>406</v>
       </c>
@@ -1829,7 +1828,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>413</v>
       </c>
@@ -1840,7 +1839,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>407</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>524</v>
       </c>
@@ -1862,44 +1861,53 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="11">
         <v>511</v>
       </c>
       <c r="B98" s="2"/>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="13">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="12">
         <v>143</v>
       </c>
       <c r="B99" s="2"/>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="13">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="12">
         <v>514</v>
       </c>
       <c r="B100" s="2"/>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="13">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
         <v>510</v>
       </c>
       <c r="B101" s="2"/>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="2" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C93" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C101" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="403"/>
+        <filter val="408"/>
+        <filter val="409"/>
+        <filter val="411"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/2025/Code MAGASIN Business Central.xlsx
+++ b/2025/Code MAGASIN Business Central.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C252BEBC-4D7D-4CF1-8E85-276EFE084ABC}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0836EBA-AE3C-4746-A782-5009476270AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2420" yWindow="2420" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>

--- a/2025/Code MAGASIN Business Central.xlsx
+++ b/2025/Code MAGASIN Business Central.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="19" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0836EBA-AE3C-4746-A782-5009476270AA}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2420" yWindow="2420" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/2025/Code MAGASIN Business Central.xlsx
+++ b/2025/Code MAGASIN Business Central.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0836EBA-AE3C-4746-A782-5009476270AA}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{D558B66C-BBCD-4D84-A823-F8D869F06087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1587B1B-F5CF-4594-BFC9-C9D36DFCC8F4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>Code Navision</t>
   </si>
@@ -353,6 +352,9 @@
   </si>
   <si>
     <t>BATAM DJERBA</t>
+  </si>
+  <si>
+    <t>enseigne</t>
   </si>
 </sst>
 </file>
@@ -426,7 +428,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -484,11 +486,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -501,21 +525,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,7 +828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" customWidth="1"/>
@@ -805,1097 +836,1500 @@
     <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>103</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" s="2" t="str">
+        <f t="shared" ref="D2:D65" si="0">IF(ISNUMBER(SEARCH("batam",C2)),"BATAM","MG")</f>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>104</v>
       </c>
       <c r="B3" s="3">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>108</v>
       </c>
       <c r="B4" s="3">
         <v>44</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>114</v>
       </c>
       <c r="B5" s="3">
         <v>59</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>119</v>
       </c>
       <c r="B6" s="3">
         <v>70</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>125</v>
       </c>
       <c r="B7" s="3">
         <v>121</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>131</v>
       </c>
       <c r="B8" s="3">
         <v>93</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>133</v>
       </c>
       <c r="B9" s="3">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>134</v>
       </c>
       <c r="B10" s="3">
         <v>120</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>135</v>
       </c>
       <c r="B11" s="3">
         <v>128</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>136</v>
       </c>
       <c r="B12" s="3">
         <v>129</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>137</v>
       </c>
       <c r="B13" s="3">
         <v>130</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>138</v>
       </c>
       <c r="B14" s="3">
         <v>132</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>139</v>
       </c>
       <c r="B15" s="3">
         <v>133</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>142</v>
       </c>
       <c r="B16" s="3">
         <v>136</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>205</v>
       </c>
       <c r="B17" s="3">
         <v>54</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>207</v>
       </c>
       <c r="B18" s="3">
         <v>7</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>301</v>
       </c>
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>304</v>
       </c>
       <c r="B20" s="3">
         <v>30</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>305</v>
       </c>
       <c r="B21" s="3">
         <v>37</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>306</v>
       </c>
       <c r="B22" s="3">
         <v>41</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>307</v>
       </c>
       <c r="B23" s="3">
         <v>49</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>308</v>
       </c>
       <c r="B24" s="3">
         <v>56</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>309</v>
       </c>
       <c r="B25" s="3">
         <v>31</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>316</v>
       </c>
       <c r="B26" s="3">
         <v>28</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>317</v>
       </c>
       <c r="B27" s="3">
         <v>39</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>318</v>
       </c>
       <c r="B28" s="3">
         <v>34</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>319</v>
       </c>
       <c r="B29" s="3">
         <v>43</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>414</v>
       </c>
       <c r="B30" s="3">
         <v>21</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>102</v>
       </c>
       <c r="B31" s="2">
         <v>14</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>106</v>
       </c>
       <c r="B32" s="2">
         <v>33</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>107</v>
       </c>
       <c r="B33" s="2">
         <v>35</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>113</v>
       </c>
       <c r="B34" s="2">
         <v>58</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>120</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>128</v>
       </c>
       <c r="B36" s="2">
         <v>98</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>129</v>
       </c>
       <c r="B37" s="2">
         <v>96</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>130</v>
       </c>
       <c r="B38" s="2">
         <v>95</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>132</v>
       </c>
       <c r="B39" s="2">
         <v>12</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>141</v>
       </c>
       <c r="B40" s="2">
         <v>135</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>145</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>201</v>
       </c>
       <c r="B42" s="2">
         <v>2</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>202</v>
       </c>
       <c r="B43" s="2">
         <v>36</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>203</v>
       </c>
       <c r="B44" s="2">
         <v>42</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>204</v>
       </c>
       <c r="B45" s="2">
         <v>48</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="11" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>206</v>
       </c>
       <c r="B46" s="2">
         <v>5</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>208</v>
       </c>
       <c r="B47" s="2">
         <v>8</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>209</v>
       </c>
       <c r="B48" s="2">
         <v>9</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>210</v>
       </c>
       <c r="B49" s="2">
         <v>55</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>213</v>
       </c>
       <c r="B50" s="2">
         <v>57</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>214</v>
       </c>
       <c r="B51" s="2">
         <v>60</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>217</v>
       </c>
       <c r="B52" s="2">
         <v>85</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>218</v>
       </c>
       <c r="B53" s="2">
         <v>86</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>220</v>
       </c>
       <c r="B54" s="2">
         <v>79</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>303</v>
       </c>
       <c r="B55" s="2">
         <v>26</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="11" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>311</v>
       </c>
       <c r="B56" s="2">
         <v>81</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>401</v>
       </c>
       <c r="B57" s="2">
         <v>10</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>402</v>
       </c>
       <c r="B58" s="2">
         <v>19</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>403</v>
       </c>
       <c r="B59" s="2">
         <v>23</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="11" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>404</v>
       </c>
       <c r="B60" s="2">
         <v>3</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>405</v>
       </c>
       <c r="B61" s="2">
         <v>38</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="11" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>408</v>
       </c>
       <c r="B62" s="2">
         <v>4</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="11" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>409</v>
       </c>
       <c r="B63" s="2">
         <v>50</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="11" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>412</v>
       </c>
       <c r="B64" s="2">
         <v>122</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D64" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>415</v>
       </c>
       <c r="B65" s="2"/>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="11" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>501</v>
       </c>
       <c r="B66" s="2">
         <v>11</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="11" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66" s="2" t="str">
+        <f t="shared" ref="D66:D101" si="1">IF(ISNUMBER(SEARCH("batam",C66)),"BATAM","MG")</f>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>502</v>
       </c>
       <c r="B67" s="2">
         <v>20</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="11" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>503</v>
       </c>
       <c r="B68" s="2">
         <v>25</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>504</v>
       </c>
       <c r="B69" s="2">
         <v>27</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="11" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>506</v>
       </c>
       <c r="B70" s="2">
         <v>40</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="11" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>507</v>
       </c>
       <c r="B71" s="2">
         <v>45</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="11" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>508</v>
       </c>
       <c r="B72" s="2">
         <v>51</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="11" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>509</v>
       </c>
       <c r="B73" s="2">
         <v>6</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>515</v>
       </c>
       <c r="B74" s="2"/>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D74" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>517</v>
       </c>
       <c r="B75" s="2">
         <v>123</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="11" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>518</v>
       </c>
       <c r="B76" s="2">
         <v>124</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D76" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>519</v>
       </c>
       <c r="B77" s="2">
         <v>126</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D77" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>521</v>
       </c>
       <c r="B78" s="2"/>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>523</v>
       </c>
       <c r="B79" s="2">
         <v>18</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="11" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D79" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>525</v>
       </c>
       <c r="B80" s="2">
         <v>131</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="11" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>140</v>
       </c>
       <c r="B81" s="2">
         <v>134</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D81" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>111</v>
       </c>
       <c r="B82" s="2">
         <v>61</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="11" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>112</v>
       </c>
       <c r="B83" s="2">
         <v>63</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D83" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>117</v>
       </c>
       <c r="B84" s="2">
         <v>68</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="11" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D84" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>116</v>
       </c>
       <c r="B85" s="2">
         <v>66</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D85" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>121</v>
       </c>
       <c r="B86" s="2">
         <v>75</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="11" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>122</v>
       </c>
       <c r="B87" s="2">
         <v>87</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D87" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>215</v>
       </c>
       <c r="B88" s="2">
         <v>73</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="11" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D88" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>219</v>
       </c>
       <c r="B89" s="2">
         <v>89</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="11" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D89" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>312</v>
       </c>
       <c r="B90" s="2">
         <v>74</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="11" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D90" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>313</v>
       </c>
       <c r="B91" s="2">
         <v>83</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="11" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D91" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>320</v>
       </c>
       <c r="B92" s="2">
         <v>56</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="D92" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="16" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>406</v>
       </c>
       <c r="B93" s="2">
         <v>46</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="13" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="D93" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="16" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>411</v>
       </c>
       <c r="B94" s="2">
         <v>84</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="13" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D94" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>413</v>
       </c>
       <c r="B95" s="2">
         <v>91</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D95" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>407</v>
       </c>
       <c r="B96" s="2">
         <v>47</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="14" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D96" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>MG</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>524</v>
       </c>
       <c r="B97" s="2">
         <v>127</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="11">
+      <c r="D97" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="8">
         <v>511</v>
       </c>
       <c r="B98" s="2"/>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="14" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
+      <c r="D98" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="9">
         <v>143</v>
       </c>
       <c r="B99" s="2"/>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="14" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="12">
+      <c r="D99" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="9">
         <v>514</v>
       </c>
       <c r="B100" s="2"/>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="14" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+      <c r="D100" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="9">
         <v>510</v>
       </c>
       <c r="B101" s="2"/>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="14" t="s">
         <v>103</v>
+      </c>
+      <c r="D101" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>BATAM</v>
       </c>
     </row>
   </sheetData>
@@ -1915,22 +2349,22 @@
       </c>
     </row>
     <row r="3" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C3" s="9">
+      <c r="C3" s="6">
         <v>511</v>
       </c>
     </row>
     <row r="4" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C4" s="10">
+      <c r="C4" s="7">
         <v>143</v>
       </c>
     </row>
     <row r="5" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C5" s="10">
+      <c r="C5" s="7">
         <v>514</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C6" s="10">
+      <c r="C6" s="7">
         <v>510</v>
       </c>
     </row>
